--- a/data/Negociado_de_Policia/npprDS_ofensores_agrupados.xlsx
+++ b/data/Negociado_de_Policia/npprDS_ofensores_agrupados.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gnper\Documents\ViolenciaGeneroPR\data\Negociado_de_Policia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DA6E3A5-83FE-447F-B4D2-DDA6BEBE6F80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{065D6DDE-B3F8-4D12-B34C-BEE880D8AA0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5592" yWindow="1896" windowWidth="17280" windowHeight="9420" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="13056" firstSheet="4" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2019" sheetId="15" r:id="rId1"/>
@@ -20,6 +20,7 @@
     <sheet name="2023" sheetId="12" r:id="rId5"/>
     <sheet name="2024" sheetId="10" r:id="rId6"/>
     <sheet name="2025" sheetId="16" r:id="rId7"/>
+    <sheet name="2026" sheetId="17" r:id="rId8"/>
   </sheets>
   <calcPr calcId="152511"/>
   <extLst>
@@ -31,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="6">
   <si>
     <t>Mujeres</t>
   </si>
@@ -767,4 +768,61 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B4012BD-924F-49BF-974D-1F830784665C}">
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="17.33203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2">
+        <v>13</v>
+      </c>
+      <c r="C2">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3">
+        <v>98</v>
+      </c>
+      <c r="C3">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4">
+        <v>49</v>
+      </c>
+      <c r="C4">
+        <v>203</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>